--- a/data/demand_template.xlsx
+++ b/data/demand_template.xlsx
@@ -1,40 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HELDE\Dropbox\git_helder\aggregate_planing\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97B84A4C-6A20-42AF-BC9D-806835B6D07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Demand" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demand" sheetId="1" r:id="rId1"/>
+    <sheet name="Demand (2)" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="15">
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>JAN</t>
+  </si>
+  <si>
+    <t>FEV</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>MAI</t>
+  </si>
+  <si>
+    <t>JUN</t>
+  </si>
+  <si>
+    <t>JUL</t>
+  </si>
+  <si>
+    <t>AGO</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>NOV</t>
+  </si>
+  <si>
+    <t>DEZ</t>
+  </si>
+  <si>
+    <t>JAN_95</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -42,85 +117,143 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,148 +541,360 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>380</v>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="8">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="8">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="8">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="8">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="11">
+        <v>241</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{586F8FD9-0DCC-4488-8393-91AB43882598}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="5">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="6"/>
+      <c r="B4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="8">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="9">
+        <v>95</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2"/>
+      <c r="B14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="11">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="8">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="8">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="8">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="8">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="8">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="9">
+        <v>96</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="8">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="8">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="8">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="6"/>
+      <c r="B25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="8">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="2"/>
+      <c r="B26" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="11">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
